--- a/docs/Zusammenfassung-Vögel.xlsx
+++ b/docs/Zusammenfassung-Vögel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\ssr\projects\sybit\coding-camp-2026\Coding-Camp-2026\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{968ABA49-FCDD-4DFD-B487-F112DD3EE8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DB833E-A8C4-4A37-B0A1-B6C11F6C5E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="34044" windowHeight="15792" xr2:uid="{1D3BA5F8-F482-424B-8A00-76D0D0349D6C}"/>
   </bookViews>
@@ -646,9 +646,6 @@
     <t>Bild</t>
   </si>
   <si>
-    <t>https://www.nabu.de/tiere-und-pflanzen/voegel/portraets/eichelhaeher.html</t>
-  </si>
-  <si>
     <t>XC1075235</t>
   </si>
   <si>
@@ -1022,16 +1019,27 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>https://www.nabu.de/tiere-und-pflanzen/voegel/portraets/eichelhaeher/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1054,14 +1062,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
@@ -1514,7 +1525,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1537,7 +1548,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
@@ -1548,19 +1559,19 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -1572,18 +1583,18 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
@@ -1595,18 +1606,18 @@
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -1618,18 +1629,18 @@
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>22</v>
@@ -1641,13 +1652,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1661,13 +1672,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1681,18 +1692,18 @@
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>31</v>
@@ -1704,13 +1715,13 @@
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1724,18 +1735,18 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -1747,13 +1758,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1767,13 +1778,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1787,13 +1798,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1807,13 +1818,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1827,13 +1838,13 @@
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1847,13 +1858,13 @@
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1867,13 +1878,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="G17" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1887,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1907,13 +1918,13 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1927,13 +1938,13 @@
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1947,13 +1958,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1967,13 +1978,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1987,18 +1998,18 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>76</v>
@@ -2010,13 +2021,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2030,13 +2041,13 @@
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2050,13 +2061,13 @@
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2070,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2090,18 +2101,18 @@
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>91</v>
@@ -2113,13 +2124,13 @@
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2133,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2153,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2173,13 +2184,13 @@
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
@@ -2193,13 +2204,13 @@
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
@@ -2213,13 +2224,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="G34" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
@@ -2233,13 +2244,13 @@
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -2253,13 +2264,13 @@
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
@@ -2273,13 +2284,13 @@
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
@@ -2293,13 +2304,13 @@
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -2313,13 +2324,13 @@
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="G39" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -2333,13 +2344,13 @@
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
@@ -2353,13 +2364,13 @@
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
@@ -2373,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
@@ -2393,13 +2404,13 @@
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
@@ -2413,13 +2424,13 @@
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -2433,13 +2444,13 @@
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
@@ -2453,13 +2464,13 @@
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
@@ -2473,13 +2484,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
@@ -2493,13 +2504,13 @@
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="G48" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
@@ -2513,13 +2524,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
@@ -2533,13 +2544,13 @@
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
@@ -2553,13 +2564,13 @@
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
@@ -2573,13 +2584,13 @@
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="G52" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
@@ -2593,13 +2604,13 @@
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
@@ -2613,13 +2624,13 @@
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
@@ -2633,13 +2644,13 @@
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
@@ -2653,13 +2664,13 @@
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
@@ -2673,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="G57" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
@@ -2693,13 +2704,13 @@
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
@@ -2713,13 +2724,13 @@
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="G59" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
@@ -2733,13 +2744,13 @@
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
@@ -2753,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
@@ -2773,19 +2784,22 @@
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="G62" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{82AD7D88-BDBF-4536-A03E-9C0A1EFBA6BC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
